--- a/Nhom01/SE_9/SE_9_Nhom01_UserStory.xlsx
+++ b/Nhom01/SE_9/SE_9_Nhom01_UserStory.xlsx
@@ -522,7 +522,7 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>Acceptance criteria theo rubric môn học</t>
+          <t>Tiêu chí nghiệm thu theo yêu cầu môn học</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
@@ -559,7 +559,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>At least 8 stories on the hand-in slide and 10 on the objective slide.</t>
+          <t>Có ít nhất 8 câu chuyện người dùng ở trang bàn giao và ít nhất 10 câu ở trang mục tiêu môn học.</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -574,7 +574,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Rows 2–17</t>
+          <t>US-001–US-016</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Each follows As a [role], I want [goal], so that [benefit].</t>
+          <t>Mỗi câu chuyện theo mẫu: “Với vai trò [vai trò], tôi muốn [mục tiêu], để [lợi ích]”.</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Columns B:D, rows 2–17</t>
+          <t>US-001–US-016</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Each is independent enough for one sprint, valuable, small and testable.</t>
+          <t>Mỗi câu chuyện đủ độc lập để làm trong một đợt phát triển, có giá trị, đủ nhỏ và kiểm thử được.</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Rows 2–17; estimates in Product Backlog</t>
+          <t>US-001–US-016; PBI-001–PBI-026</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Each names its epic, feature and raw-wish ID.</t>
+          <t>Mỗi câu chuyện nêu nhóm nghiệp vụ, tính năng và mã mong muốn gốc tương ứng.</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Columns E:F, rows 2–17</t>
+          <t>US-001–US-016; RAW-001–RAW-012; EP-001–EP-005; FE-001–FE-026</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Each has MoSCoW priority with Must for v1.0, plus Should, Could or Won’t for this release.</t>
+          <t>Mỗi câu chuyện có mức ưu tiên theo bốn mức: Bắt buộc cho phiên bản 1.0; Nên có, Có thể có hoặc Không đưa vào cho đợt phát hành này.</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Column G, rows 2–17</t>
+          <t>US-001–US-016</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
